--- a/manuscript/submission_data/source_data/Source_Data_Figure_5.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Figure_5.xlsx
@@ -1,18 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Panel_E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Panel_F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_D" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,6 +428,435 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>figure_label</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Figure 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>panel_label</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>panel_title</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nested evidence chain and denominator flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>final_placement</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>shared_input_bundle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>original_bundle_label</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>manuscript/figure_data/fig05_evidence_chain_summary.tsv</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>found</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>stage_id</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>stage_label</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>parent_stage_id</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>parent_n</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>interpretive_role</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>manuscript_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>retained_archive</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Retained public-genome archive</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Complete retained archive after accession, QC and provenance filters</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Defines archive composition and missingness bounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>interpretable_event_phenotype</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Interpretable event/phenotype frame</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>retained_archive</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Records with either structurally resolved disruption or intact-locus boundary call</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Main manuscript-facing event and phenotype frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>noninterpretable_uncertain</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Non-interpretable or uncertain records</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>retained_archive</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Records without a supported interpretable prn endpoint</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Enter missingness bounds rather than event-concentration denominators</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>structurally_resolved_disrupted</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Structurally resolved disrupted event calls</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>interpretable_event_phenotype</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Resolved disrupted prn calls assigned to 14 frozen event classes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Event-concentration and recurrent-route denominator</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>intact_boundary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Intact-locus boundary calls</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>interpretable_event_phenotype</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Genome-intact prn boundary without direct protein-expression proof</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phenotype-tier comparison boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tier1a_phenotype_bridge</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tier 1a junction-class phenotype bridge</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>structurally_resolved_disrupted</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Read-backed event classes linked to published PRN non-expression-compatible lesion classes</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Highest phenotype-plausibility bridge in the present genome calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>other_disrupted_phenotype_tiers</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tier 1b-3 disrupted phenotype tiers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>structurally_resolved_disrupted</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Disrupted event classes with lesion-class-only, plausible genome-disruption or genome-only phenotype support</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lower phenotype-plausibility disrupted calls retained as bounded genome evidence</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -491,7 +918,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -539,7 +966,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -10016,902 +10443,6 @@
       <c r="X92" t="inlineStr">
         <is>
           <t>United States</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="62" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
-    <col width="62" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>figure_label</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Figure 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>panel_label</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>panel_title</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Published PRN phenotype bridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>final_placement</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>shared_input_bundle</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>original_bundle_label</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>manuscript/figure_data/biology_bridge_external_context.tsv</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>found</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>context_id</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>country_or_region</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>n_total_or_frame</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>n_prn_producing</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>n_prn_deficient</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>n_amr_or_a2047g</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>headline</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>interpretive_role</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>japan_otsuka_2012_expression_bridge</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1990-2010 isolate collection</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PRN immunoblot plus prn mechanism sequencing</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Thirty-three of 121 isolates were PRN-negative; 24 carried an 84-bp signal-sequence deletion and nine carried IS481 insertions with ACTAGG direct repeats.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>phenotype-genotype bridge for deletion and IS481 lesion classes</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Otsuka et al. PLoS ONE 2012;7:e31985. doi:10.1371/journal.pone.0031985</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>usa_pawloski_2014_expression_bridge</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1935-2012 surveillance isolate collection</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Western blot plus prn sequencing</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>PRN deficiency was confirmed in 306 isolates, including 276 prn::IS481 isolates, and exceeded half of tested isolates by 2012.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>phenotype-genotype bridge for recurrent IS481-mediated PRN loss</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Pawloski et al. Clin. Vaccine Immunol. 2014;21:119-125. doi:10.1128/CVI.00717-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>australia_lam_2014_expression_bridge</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2008-2012 rise in PRN-negative isolates</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Western immunoblot plus prn/promoter mechanism assessment</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Ninety-six of 320 isolates were PRN-negative; among 80 mechanism-resolved PRN-negative isolates, 77 had insertion-sequence lesions, while 16 PRN-negative isolates lacked an obvious prn/promoter change.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>phenotype-genotype bridge and caution that protein testing can reveal lesions missed by locus inspection</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Lam et al. Emerg. Infect. Dis. 2014;20:626-633. doi:10.3201/eid2004.131478</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>europe_eupert_1998_2015_expression_bridge</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>EUpert I-IV, 1998-2015</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ELISA antigen-expression testing across European isolate collections</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PRN-deficient frequency increased from 1.0% in 1998-2001 to 24.9% in 2012-2015; IS481 and promoter inversion were the largest mechanism classes.</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>multi-country phenotype-genotype bridge for recurrent PRN loss</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Barkoff et al. Euro Surveill. 2019;24:1700832. doi:10.2807/1560-7917.ES.2019.24.7.1700832</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>france_2023_2024_resurgence</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>June 2023-April 2024</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>national-reference-centre isolate phenotype and WGS</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Post-pandemic resurgence was dominated by pertactin-producing isolates despite one macrolide-resistant isolate.</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>post-pandemic counterexample to a one-way PRN-loss resurgence model</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Rodrigues et al. Euro Surveill. 2024;29:2400459. doi:10.2807/1560-7917.ES.2024.29.31.2400459</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>belgium_2022_2023_expression</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2022-2023, after pre-pandemic PRN-negative peak</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>national-reference-centre PRN expression testing and WGS</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>All 94 tested post-COVID isolates expressed pertactin after a pre-pandemic PRN-negative peak around 65%.</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>post-pandemic counterexample and phenotype bridge</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Martini et al. Microbiol. Spectr. 2026;14:e01535-25. doi:10.1128/spectrum.01535-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>belgium_2000_2023_expression_bridge</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2000-2023 national-reference-centre collection</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PRN ELISA plus WGS mechanism assessment</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Among 432 isolates tested by PRN ELISA, 180 were PRN-negative; WGS on 416 isolates linked loss to IS481, deletion, premature stop, promoter inversion and promoter deletion classes.</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>phenotype-genotype bridge and post-COVID boundary</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Martini et al. Microbiol. Spectr. 2026;14:e01535-25. doi:10.1128/spectrum.01535-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>netherlands_2023_2024_prn_positive_boundary</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2023-2024 resurgence</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>official national surveillance report</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>The reported PRN-deficient fraction fell to 7% in 2023-2024 after 13% in 2015-2017 and 25% in 2018-2020; no 23S rRNA A2047G macrolide-resistance mutation was detected.</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>post-pandemic counterexample and AMR-negative boundary condition</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>RIVM. Resurgence of Bordetella pertussis in the Netherlands in 2023-2024. Report 2025-0092. https://www.rivm.nl/bibliotheek/rapporten/2025-0092.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>slovenia_2002_2020_expression</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2002-2020; high-frequency period 2017-2020</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ELISA antigen-expression testing plus prn WGS</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Overall 48 of 123 isolates were PRN-deficient; 44 of 49 isolates from 2017-2020 did not express PRN.</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>direct PRN-expression bridge for genome-defined prn lesions</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Barkoff et al. Emerg. Infect. Dis. 2024;30:2429-2432. doi:10.3201/eid3011.231393</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>slovenia_2024_resurgence_boundary</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2024 epidemic</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>national epidemic isolate report</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>The 2024 epidemic report found no pertactin-deficient or macrolide-resistant isolates.</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>post-pandemic counterexample after an earlier high PRN-deficient period</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Kastrin et al. Clin. Microbiol. Infect. 2025. doi:10.1016/j.cmi.2025.04.016</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>beijing_2022_2023_amr_antigen_deficiency</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Beijing, China</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2022-2023</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>sentinel-hospital isolate WGS and antimicrobial susceptibility</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>All isolates were erythromycin resistant with the same 23S mutation background; 30 were Prn deficient and two were Fha deficient.</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>AMR and antigen-deficiency boundary condition, not a direct vaccine-programme contrast</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Zhou et al. China CDC Wkly. 2024;6:437-441. doi:10.46234/ccdcw2024.085</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>shanghai_2018_2024_mr_mt28</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Shanghai, China</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2018-2024</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>active-surveillance isolate WGS and antimicrobial susceptibility</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>MT28 increased from 16% before 2020 to 61.17% after 2020; post-2020 MT28 isolates were macrolide resistant, ptxP3-associated and carried prn150 antigen profiles.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>AMR and lineage-background context, especially for China-dominated post-pandemic signals</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Xu et al. J. Clin. Microbiol. 2025;63:e0106425. doi:10.1128/jcm.01064-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>global_mr_mt28_post_pandemic</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Global, enriched for China and post-pandemic genomes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>pre-, during and post-COVID-19 comparison</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>global genomic surveillance and AMR/antigen-profile analysis</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>8117</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>MR-MT28 expanded in eastern China and spread internationally; most non-Chinese MR-MT28 isolates were PRN-deficient.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>lineage and AMR context for interpreting post-pandemic public-genome signals</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Zhang et al. J. Infect. 2026;92:106718. doi:10.1016/j.jinf.2026.106718</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>eu_eea_2024_resurgence</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>EU/EEA</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>regional epidemiological surveillance report</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>209674</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>EU/EEA reported 209,674 pertussis cases in 2024, with resurgence attributed to multiple immunity, behaviour and testing factors.</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>epidemiological boundary showing that resurgence is not reducible to PRN loss</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>ECDC. Annual epidemiological report for 2024: Pertussis. 2026.</t>
         </is>
       </c>
     </row>
@@ -10926,20 +10457,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="10" max="10"/>
     <col width="62" customWidth="1" min="11" max="11"/>
+    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="62" customWidth="1" min="13" max="13"/>
+    <col width="62" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10986,7 +10520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMR and lineage-background overlay</t>
+          <t>Published PRN phenotype bridge and route-family tiers</t>
         </is>
       </c>
     </row>
@@ -11042,7 +10576,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manuscript/figure_data/biology_bridge_internal_sensitivity.tsv</t>
+          <t>manuscript/figure_data/biology_bridge_external_context.tsv</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11055,836 +10589,1938 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>analysis_layer</t>
+          <t>context_id</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>group_variable</t>
+          <t>country_or_region</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>group_value</t>
+          <t>period</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>n_records</t>
+          <t>evidence_type</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>n_prn_interpretable</t>
+          <t>n_total_or_frame</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>n_prn_disrupted</t>
+          <t>n_prn_producing</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>prn_disrupted_fraction_among_interpretable</t>
+          <t>n_prn_deficient</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>n_gap1043</t>
+          <t>n_amr_or_a2047g</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>n_ptxP3</t>
+          <t>headline</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>n_fim3_1</t>
+          <t>interpretive_role</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>interpretation</t>
+          <t>reference</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>published_overlap</t>
+          <t>japan_otsuka_2012_expression_bridge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>prn_status_concordance</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>1990-2010 isolate collection</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+          <t>PRN immunoblot plus prn mechanism sequencing</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Thirty-three of 121 isolates were PRN-negative; 24 carried an 84-bp signal-sequence deletion and nine carried IS481 insertions with ACTAGG direct repeats.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>phenotype-genotype bridge for deletion and IS481 lesion classes</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1092 of 1174 compared rows were concordant (fraction 0.930).</t>
+          <t>Otsuka et al. PLoS ONE 2012;7:e31985. doi:10.1371/journal.pone.0031985</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>published_overlap</t>
+          <t>usa_pawloski_2014_expression_bridge</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>prn_mechanism_broad_concordance</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>1935-2012 surveillance isolate collection</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Western blot plus prn sequencing</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PRN deficiency was confirmed in 306 isolates, including 276 prn::IS481 isolates, and exceeded half of tested isolates by 2012.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>phenotype-genotype bridge for recurrent IS481-mediated PRN loss</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>311 of 515 compared rows were concordant (fraction 0.604). Broad comparison collapses published mechanism calls to IS481 versus other_or_unspecified.</t>
+          <t>Pawloski et al. Clin. Vaccine Immunol. 2014;21:119-125. doi:10.1128/CVI.00717-13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>published_overlap</t>
+          <t>australia_lam_2014_expression_bridge</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>published_PRN_status_rows</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>2008-2012 rise in PRN-negative isolates</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>Western immunoblot plus prn/promoter mechanism assessment</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ninety-six of 320 isolates were PRN-negative; among 80 mechanism-resolved PRN-negative isolates, 77 had insertion-sequence lesions, while 16 PRN-negative isolates lacked an obvious prn/promoter change.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>phenotype-genotype bridge and caution that protein testing can reveal lesions missed by locus inspection</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Rows with a published PRN-status annotation; concordance is restricted to the compared subset rather than all annotated rows.</t>
+          <t>Lam et al. Emerg. Infect. Dis. 2014;20:626-633. doi:10.3201/eid2004.131478</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>europe_eupert_1998_2015_expression_bridge</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>marker_23s_status</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>EUpert I-IV, 1998-2015</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>ELISA antigen-expression testing across European isolate collections</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.469116</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>PRN-deficient frequency increased from 1.0% in 1998-2001 to 24.9% in 2012-2015; IS481 and promoter inversion were the largest mechanism classes.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>multi-country phenotype-genotype bridge for recurrent PRN loss</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Internal 23S-marker stratum; used as support-only AMR context and not as a primary causal adjustment.</t>
+          <t>Barkoff et al. Euro Surveill. 2019;24:1700832. doi:10.2807/1560-7917.ES.2019.24.7.1700832</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>france_2023_2024_resurgence</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>marker_23s_status</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MR_A2047G</t>
+          <t>June 2023-April 2024</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>national-reference-centre isolate phenotype and WGS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0.000000</t>
-        </is>
-      </c>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>Post-pandemic resurgence was dominated by pertactin-producing isolates despite one macrolide-resistant isolate.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>post-pandemic counterexample to a one-way PRN-loss resurgence model</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Internal 23S-marker stratum; used as support-only AMR context and not as a primary causal adjustment.</t>
+          <t>Rodrigues et al. Euro Surveill. 2024;29:2400459. doi:10.2807/1560-7917.ES.2024.29.31.2400459</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>belgium_2022_2023_expression</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>marker_23s_status</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>other_23S_allele</t>
+          <t>2022-2023, after pre-pandemic PRN-negative peak</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>national-reference-centre PRN expression testing and WGS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>All 94 tested post-COVID isolates expressed pertactin after a pre-pandemic PRN-negative peak around 65%.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>post-pandemic counterexample and phenotype bridge</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Internal 23S-marker stratum; used as support-only AMR context and not as a primary causal adjustment.</t>
+          <t>Martini et al. Microbiol. Spectr. 2026;14:e01535-25. doi:10.1128/spectrum.01535-25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>belgium_2000_2023_expression_bridge</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>marker_23s_status</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unassigned</t>
+          <t>2000-2023 national-reference-centre collection</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>PRN ELISA plus WGS mechanism assessment</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>432</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.269841</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Among 432 isolates tested by PRN ELISA, 180 were PRN-negative; WGS on 416 isolates linked loss to IS481, deletion, premature stop, promoter inversion and promoter deletion classes.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>phenotype-genotype bridge and post-COVID boundary</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Internal 23S-marker stratum; used as support-only AMR context and not as a primary causal adjustment.</t>
+          <t>Martini et al. Microbiol. Spectr. 2026;14:e01535-25. doi:10.1128/spectrum.01535-25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>netherlands_2023_2024_prn_positive_boundary</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>published_sublineage</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>United States Sublineage 1</t>
+          <t>2023-2024 resurgence</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.989170</t>
-        </is>
-      </c>
+          <t>official national surveillance report</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>The reported PRN-deficient fraction fell to 7% in 2023-2024 after 13% in 2015-2017 and 25% in 2018-2020; no 23S rRNA A2047G macrolide-resistance mutation was detected.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>post-pandemic counterexample and AMR-negative boundary condition</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Published-lineage stratum; used to check whether prn disruption is simply a single AMR or lineage label.</t>
+          <t>RIVM. Resurgence of Bordetella pertussis in the Netherlands in 2023-2024. Report 2025-0092. https://www.rivm.nl/bibliotheek/rapporten/2025-0092.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>slovenia_2002_2020_expression</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>published_sublineage</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ptxP3/fim3-1</t>
+          <t>2002-2020; high-frequency period 2017-2020</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>ELISA antigen-expression testing plus prn WGS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.338323</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>Overall 48 of 123 isolates were PRN-deficient; 44 of 49 isolates from 2017-2020 did not express PRN.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>direct PRN-expression bridge for genome-defined prn lesions</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Published-lineage stratum; used to check whether prn disruption is simply a single AMR or lineage label.</t>
+          <t>Barkoff et al. Emerg. Infect. Dis. 2024;30:2429-2432. doi:10.3201/eid3011.231393</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>slovenia_2024_resurgence_boundary</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>published_sublineage</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ptxP3/fim3-2</t>
+          <t>2024 epidemic</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
+          <t>national epidemic isolate report</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.333333</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>The 2024 epidemic report found no pertactin-deficient or macrolide-resistant isolates.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>post-pandemic counterexample after an earlier high PRN-deficient period</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Published-lineage stratum; used to check whether prn disruption is simply a single AMR or lineage label.</t>
+          <t>Kastrin et al. Clin. Microbiol. Infect. 2025. doi:10.1016/j.cmi.2025.04.016</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>beijing_2022_2023_amr_antigen_deficiency</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>published_sublineage</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MR-MT28-others</t>
+          <t>2022-2023</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>sentinel-hospital isolate WGS and antimicrobial susceptibility</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.000000</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>All isolates were erythromycin resistant with the same 23S mutation background; 30 were Prn deficient and two were Fha deficient.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>AMR and antigen-deficiency boundary condition, not a direct vaccine-programme contrast</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Published-lineage stratum; used to check whether prn disruption is simply a single AMR or lineage label.</t>
+          <t>Zhou et al. China CDC Wkly. 2024;6:437-441. doi:10.46234/ccdcw2024.085</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>shanghai_2018_2024_mr_mt28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>published_sublineage</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MR-MT28-PG1</t>
+          <t>2018-2024</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>active-surveillance isolate WGS and antimicrobial susceptibility</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1.000000</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>MT28 increased from 16% before 2020 to 61.17% after 2020; post-2020 MT28 isolates were macrolide resistant, ptxP3-associated and carried prn150 antigen profiles.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>AMR and lineage-background context, especially for China-dominated post-pandemic signals</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Published-lineage stratum; used to check whether prn disruption is simply a single AMR or lineage label.</t>
+          <t>Xu et al. J. Clin. Microbiol. 2025;63:e0106425. doi:10.1128/jcm.01064-25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>global_mr_mt28_post_pandemic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>published_sublineage</t>
+          <t>Global, enriched for China and post-pandemic genomes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MR-MT28-PG2</t>
+          <t>pre-, during and post-COVID-19 comparison</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>global genomic surveillance and AMR/antigen-profile analysis</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0.000000</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>8117</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>MR-MT28 expanded in eastern China and spread internationally; most non-Chinese MR-MT28 isolates were PRN-deficient.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>lineage and AMR context for interpreting post-pandemic public-genome signals</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Published-lineage stratum; used to check whether prn disruption is simply a single AMR or lineage label.</t>
+          <t>Zhang et al. J. Infect. 2026;92:106718. doi:10.1016/j.jinf.2026.106718</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>internal_genome_context</t>
+          <t>eu_eea_2024_resurgence</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>published_sublineage</t>
+          <t>EU/EEA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MS-MT28</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>regional epidemiological surveillance report</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0.000000</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>209674</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>EU/EEA reported 209,674 pertussis cases in 2024, with resurgence attributed to multiple immunity, behaviour and testing factors.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>epidemiological boundary showing that resurgence is not reducible to PRN loss</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Published-lineage stratum; used to check whether prn disruption is simply a single AMR or lineage label.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>internal_genome_context</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>published_sublineage</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0.420354</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Published-lineage stratum; used to check whether prn disruption is simply a single AMR or lineage label.</t>
+          <t>ECDC. Annual epidemiological report for 2024: Pertussis. 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>manuscript/supplementary/Supplementary_Table_10_Event_Class_Phenotype_Evidence_Tiers.tsv</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>found</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>prn_event_id</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>mechanism_call</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>event_subcategory</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>sample_count</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>country_count</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>year_min</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>year_max</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>validation_level</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>tsd_or_flank_sequence_status</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>phenotype_evidence_tier</t>
+        </is>
+      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t>phenotype_inference</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t>supporting_external_context</t>
+        </is>
+      </c>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>caution_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>coding_disrupted_is481</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IS481 insertion</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>read_backed_targeted_validation</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Tier 1a junction-class phenotype bridge</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Read-backed junction or event-class evidence places this architecture within lesion classes repeatedly linked to PRN non-expression, but the present archive still lacks genome-by-genome expression assays.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Japan 1990-2010, United States 1935-2012, Europe 1998-2015, Belgium 2000-2023</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Treat as junction-class bridged, not genome-by-genome protein proven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov58</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Inversion / rearrangement</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>read_backed_targeted_validation</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Tier 1a junction-class phenotype bridge</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Read-backed junction or event-class evidence places this architecture within lesion classes repeatedly linked to PRN non-expression, but the present archive still lacks genome-by-genome expression assays.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Europe 1998-2015, Belgium 2000-2023</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Treat as junction-class bridged, not genome-by-genome protein proven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov91</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Inversion / rearrangement</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>read_backed_targeted_validation</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Tier 1a junction-class phenotype bridge</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Read-backed junction or event-class evidence places this architecture within lesion classes repeatedly linked to PRN non-expression, but the present archive still lacks genome-by-genome expression assays.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Europe 1998-2015, Belgium 2000-2023</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Treat as junction-class bridged, not genome-by-genome protein proven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1042</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>coding_disrupted_is481</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>IS481 insertion</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>public_longread_or_hybrid_assembly</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>public_longread_or_hybrid_assembly</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>read_interval_without_tsd</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Tier 1b lesion-class bridge only</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>The lesion class is externally linked to PRN non-expression, but this exact event class is not protein-tested here and has weaker junction-level support in the present archive summary.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Japan 1990-2010, United States 1935-2012, Europe 1998-2015, Belgium 2000-2023</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Treat as lesion-class bridged only; prioritize read-backed or expression validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1041</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>coding_disrupted_is481</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IS481 insertion</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>public_longread_or_hybrid_assembly</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>public_longread_or_hybrid_assembly</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>assembly_coordinate_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Tier 1b lesion-class bridge only</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>The lesion class is externally linked to PRN non-expression, but this exact event class is not protein-tested here and has weaker junction-level support in the present archive summary.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Japan 1990-2010, United States 1935-2012, Europe 1998-2015, Belgium 2000-2023</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Treat as lesion-class bridged only; prioritize read-backed or expression validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1045</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>coding_disrupted_is481</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>IS481 insertion</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>assembly_only</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>assembly_only</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>assembly_coordinate_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Tier 1b lesion-class bridge only</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>The lesion class is externally linked to PRN non-expression, but this exact event class is not protein-tested here and has weaker junction-level support in the present archive summary.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Japan 1990-2010, United States 1935-2012, Europe 1998-2015, Belgium 2000-2023</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Treat as lesion-class bridged only; prioritize read-backed or expression validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap54</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>coding_disrupted_is481</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>IS481 insertion</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>assembly_only</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>assembly_only</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>assembly_coordinate_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Tier 1b lesion-class bridge only</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>The lesion class is externally linked to PRN non-expression, but this exact event class is not protein-tested here and has weaker junction-level support in the present archive summary.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Japan 1990-2010, United States 1935-2012, Europe 1998-2015, Belgium 2000-2023</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Treat as lesion-class bridged only; prioritize read-backed or expression validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov94</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Inversion / rearrangement</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>public_longread_or_hybrid_assembly</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>public_longread_or_hybrid_assembly</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>not_recovered_current_public_data</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Tier 1b lesion-class bridge only</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>The lesion class is externally linked to PRN non-expression, but this exact event class is not protein-tested here and has weaker junction-level support in the present archive summary.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Europe 1998-2015, Belgium 2000-2023</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Treat as lesion-class bridged only; prioritize read-backed or expression validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>prn_evt_other_disruption__insertion_like__gap1042</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>coding_disrupted_other</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Other disruptions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>read_backed_targeted_validation</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Tier 2 genome-disruption plausible</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Coding disruption is structurally compatible with PRN non-expression and has strong genome evidence, but no exact event-class expression bridge was identified for this archive summary.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>External phenotype bridge supports the broader disrupted-locus interpretation rather than this exact event label</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Retain as genome-defined disruption until paired PRN expression assays are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>prn_evt_other_disruption__insertion_like__gap1041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>coding_disrupted_other</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Other disruptions</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>read_backed_targeted_validation</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Tier 2 genome-disruption plausible</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Coding disruption is structurally compatible with PRN non-expression and has strong genome evidence, but no exact event-class expression bridge was identified for this archive summary.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>External phenotype bridge supports the broader disrupted-locus interpretation rather than this exact event label</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Retain as genome-defined disruption until paired PRN expression assays are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>coding_disrupted_other</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Other disruptions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>read_backed_targeted_validation</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>target_site_duplication_recovered</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Tier 2 genome-disruption plausible</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Coding disruption is structurally compatible with PRN non-expression and has strong genome evidence, but no exact event-class expression bridge was identified for this archive summary.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>External phenotype bridge supports the broader disrupted-locus interpretation rather than this exact event label</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Retain as genome-defined disruption until paired PRN expression assays are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>prn_evt_other_disruption__insertion_like__gap1044</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>coding_disrupted_other</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Other disruptions</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>read_validation_unresolved</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>read_validation_unresolved</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>assembly_coordinate_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Tier 3 genome-only disruption</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Genome architecture supports disruption, but phenotype inference remains indirect and event-specific protein evidence is currently absent.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>External phenotype bridge supports the broader disrupted-locus interpretation rather than this exact event label</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Retain as genome-defined disruption until paired PRN expression assays are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>prn_evt_other_disruption__insertion_like__gap1045</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>coding_disrupted_other</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Other disruptions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>read_validation_unresolved</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>read_validation_unresolved</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>assembly_coordinate_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Tier 3 genome-only disruption</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Genome architecture supports disruption, but phenotype inference remains indirect and event-specific protein evidence is currently absent.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>External phenotype bridge supports the broader disrupted-locus interpretation rather than this exact event label</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Retain as genome-defined disruption until paired PRN expression assays are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>prn_evt_other_disruption__insertion_like__gap204</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>coding_disrupted_other</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Other disruptions</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>assembly_only</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>assembly_only</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>assembly_coordinate_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Tier 3 genome-only disruption</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Genome architecture supports disruption, but phenotype inference remains indirect and event-specific protein evidence is currently absent.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>External phenotype bridge supports the broader disrupted-locus interpretation rather than this exact event label</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Retain as genome-defined disruption until paired PRN expression assays are available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>prn_evt_intact</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>intact</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Intact locus</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>genome_intact_boundary</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Boundary only, not expression-proven</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>A genome-intact prn locus does not prove PRN production at the protein level in this archive.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Australia 2008-2012 and Belgium 2000-2023 report PRN-negative isolates without an obvious genome-only prn lesion.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Do not treat intact-locus calls as direct PRN-positive phenotype assignments.</t>
         </is>
       </c>
     </row>
@@ -11899,59 +12535,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="33" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="36" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="23" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="35" customWidth="1" min="21" max="21"/>
-    <col width="31" customWidth="1" min="22" max="22"/>
-    <col width="31" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
-    <col width="23" customWidth="1" min="28" max="28"/>
-    <col width="23" customWidth="1" min="29" max="29"/>
-    <col width="27" customWidth="1" min="30" max="30"/>
-    <col width="31" customWidth="1" min="31" max="31"/>
-    <col width="37" customWidth="1" min="32" max="32"/>
-    <col width="33" customWidth="1" min="33" max="33"/>
-    <col width="33" customWidth="1" min="34" max="34"/>
-    <col width="38" customWidth="1" min="35" max="35"/>
-    <col width="26" customWidth="1" min="36" max="36"/>
-    <col width="23" customWidth="1" min="37" max="37"/>
-    <col width="27" customWidth="1" min="38" max="38"/>
-    <col width="33" customWidth="1" min="39" max="39"/>
-    <col width="29" customWidth="1" min="40" max="40"/>
-    <col width="29" customWidth="1" min="41" max="41"/>
-    <col width="34" customWidth="1" min="42" max="42"/>
-    <col width="22" customWidth="1" min="43" max="43"/>
-    <col width="24" customWidth="1" min="44" max="44"/>
-    <col width="28" customWidth="1" min="45" max="45"/>
-    <col width="34" customWidth="1" min="46" max="46"/>
-    <col width="30" customWidth="1" min="47" max="47"/>
-    <col width="30" customWidth="1" min="48" max="48"/>
-    <col width="35" customWidth="1" min="49" max="49"/>
-    <col width="23" customWidth="1" min="50" max="50"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11998,7 +12594,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Missingness-estimator percentage-point contrasts</t>
+          <t>Validation evidence stack</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12650,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manuscript/figure_data/selected_country/selected_country_dr_missingness_summary.tsv</t>
+          <t>manuscript/figure_data/caller_validation_sensitivity_summary.tsv</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -12067,3070 +12663,612 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>country_iso3</t>
+          <t>audit_section</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>country_name</t>
+          <t>evidence_layer</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>previous_epoch_id</t>
+          <t>comparison_or_risk</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>next_epoch_id</t>
+          <t>n_overlap_rows</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>n_total_previous_epoch</t>
+          <t>n_compared_rows</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>n_total_next_epoch</t>
+          <t>n_supporting_rows</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>n_observed_previous_epoch</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>n_observed_next_epoch</t>
+          <t>main_result</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>propensity_median_interpretable</t>
+          <t>supporting_table</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>propensity_q05_interpretable</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>propensity_q95_interpretable</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>propensity_median_missing</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>propensity_q05_missing</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>propensity_q95_missing</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>propensity_crossfit_fraction</t>
-        </is>
-      </c>
-      <c r="P12" s="1" t="inlineStr">
-        <is>
-          <t>outcome_crossfit_fraction_observed</t>
-        </is>
-      </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>p01_weight_truncation</t>
-        </is>
-      </c>
-      <c r="R12" s="1" t="inlineStr">
-        <is>
-          <t>p99_weight_truncation</t>
-        </is>
-      </c>
-      <c r="S12" s="1" t="inlineStr">
-        <is>
-          <t>p05_weight_truncation</t>
-        </is>
-      </c>
-      <c r="T12" s="1" t="inlineStr">
-        <is>
-          <t>p95_weight_truncation</t>
-        </is>
-      </c>
-      <c r="U12" s="1" t="inlineStr">
-        <is>
-          <t>dr_estimator_label</t>
-        </is>
-      </c>
-      <c r="V12" s="1" t="inlineStr">
-        <is>
-          <t>sign_stable_across_estimators</t>
-        </is>
-      </c>
-      <c r="W12" s="1" t="inlineStr">
-        <is>
-          <t>consistent_nonzero_delta_sign</t>
-        </is>
-      </c>
-      <c r="X12" s="1" t="inlineStr">
-        <is>
-          <t>weight_mean</t>
-        </is>
-      </c>
-      <c r="Y12" s="1" t="inlineStr">
-        <is>
-          <t>weight_max</t>
-        </is>
-      </c>
-      <c r="Z12" s="1" t="inlineStr">
-        <is>
-          <t>weight_q95</t>
-        </is>
-      </c>
-      <c r="AA12" s="1" t="inlineStr">
-        <is>
-          <t>weight_q99</t>
-        </is>
-      </c>
-      <c r="AB12" s="1" t="inlineStr">
-        <is>
-          <t>weight_fraction_gt_10</t>
-        </is>
-      </c>
-      <c r="AC12" s="1" t="inlineStr">
-        <is>
-          <t>weight_fraction_gt_20</t>
-        </is>
-      </c>
-      <c r="AD12" s="1" t="inlineStr">
-        <is>
-          <t>previous_naive_prevalence</t>
-        </is>
-      </c>
-      <c r="AE12" s="1" t="inlineStr">
-        <is>
-          <t>previous_ipw_cap20_prevalence</t>
-        </is>
-      </c>
-      <c r="AF12" s="1" t="inlineStr">
-        <is>
-          <t>previous_ipw_untruncated_prevalence</t>
-        </is>
-      </c>
-      <c r="AG12" s="1" t="inlineStr">
-        <is>
-          <t>previous_ipw_p01_p99_prevalence</t>
-        </is>
-      </c>
-      <c r="AH12" s="1" t="inlineStr">
-        <is>
-          <t>previous_ipw_p05_p95_prevalence</t>
-        </is>
-      </c>
-      <c r="AI12" s="1" t="inlineStr">
-        <is>
-          <t>previous_overlap_observed_prevalence</t>
-        </is>
-      </c>
-      <c r="AJ12" s="1" t="inlineStr">
-        <is>
-          <t>previous_aipw_prevalence</t>
-        </is>
-      </c>
-      <c r="AK12" s="1" t="inlineStr">
-        <is>
-          <t>next_naive_prevalence</t>
-        </is>
-      </c>
-      <c r="AL12" s="1" t="inlineStr">
-        <is>
-          <t>next_ipw_cap20_prevalence</t>
-        </is>
-      </c>
-      <c r="AM12" s="1" t="inlineStr">
-        <is>
-          <t>next_ipw_untruncated_prevalence</t>
-        </is>
-      </c>
-      <c r="AN12" s="1" t="inlineStr">
-        <is>
-          <t>next_ipw_p01_p99_prevalence</t>
-        </is>
-      </c>
-      <c r="AO12" s="1" t="inlineStr">
-        <is>
-          <t>next_ipw_p05_p95_prevalence</t>
-        </is>
-      </c>
-      <c r="AP12" s="1" t="inlineStr">
-        <is>
-          <t>next_overlap_observed_prevalence</t>
-        </is>
-      </c>
-      <c r="AQ12" s="1" t="inlineStr">
-        <is>
-          <t>next_aipw_prevalence</t>
-        </is>
-      </c>
-      <c r="AR12" s="1" t="inlineStr">
-        <is>
-          <t>delta_naive_prevalence</t>
-        </is>
-      </c>
-      <c r="AS12" s="1" t="inlineStr">
-        <is>
-          <t>delta_ipw_cap20_prevalence</t>
-        </is>
-      </c>
-      <c r="AT12" s="1" t="inlineStr">
-        <is>
-          <t>delta_ipw_untruncated_prevalence</t>
-        </is>
-      </c>
-      <c r="AU12" s="1" t="inlineStr">
-        <is>
-          <t>delta_ipw_p01_p99_prevalence</t>
-        </is>
-      </c>
-      <c r="AV12" s="1" t="inlineStr">
-        <is>
-          <t>delta_ipw_p05_p95_prevalence</t>
-        </is>
-      </c>
-      <c r="AW12" s="1" t="inlineStr">
-        <is>
-          <t>delta_overlap_observed_prevalence</t>
-        </is>
-      </c>
-      <c r="AX12" s="1" t="inlineStr">
-        <is>
-          <t>delta_aipw_prevalence</t>
+          <t>interpretation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>caller_validation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>PRN status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>aus_wp_only</t>
+          <t>repo PRN status versus published PRN status or phenotype annotation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>aus_ap_with_prn</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0.930</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>repo negative, published negative=515; repo negative, published positive=7; repo positive, published negative=75; repo positive, published positive=577</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.9633176862035823</t>
+          <t>Supplementary Table 7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.04320102231314861</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.999</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>0.39469466542564663</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>0.020483395378890046</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.9694661403230205</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>649.3414327754952</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>25.755143357068953</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>aipw_with_crossfit_when_available</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>decrease</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>29.504722091692763</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>25.755143357068953</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>649.3414327754952</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>0.07894736842105263</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>0.07894736842105263</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>0.6153846153846154</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>0.7424079164473865</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>0.7424079164473865</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>0.7424079164473865</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0.7424079164473865</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>0.8701233534660194</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>0.6839788394566205</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>0.5289202894309796</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>0.07220004853745747</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>0.10596285631232978</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0.5306612695701515</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0.3754693599188319</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-25.87184658671461</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.2953846153846154</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>-0.2134876270164069</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-0.670207867909929</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>-0.6364450601350566</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>-0.211746646877235</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>-0.49465399354718753</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>-26.555825426171232</t>
+          <t>Primary caller validation layer; discordant rows are retained as audit flags.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>caller_validation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>broad mechanism</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap</t>
+          <t>repo broad mechanism versus published broad mechanism among PRN-negative concordant rows</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jpn_ap_without_prn</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>311</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>repo IS481 / published IS481 = 291; repo other_or_unspecified / published IS481 = 148; repo IS481 / published other_or_unspecified = 34; repo other_or_unspecified / published other_or_unspecified = 20</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.934299578124003</t>
+          <t>Supplementary Table 7</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.49587920611145025</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.999</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>0.906894279591171</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.999</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>7.370478157664402</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2.046184166263543</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>aipw_with_crossfit_when_available</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>decrease</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1.3112273605242157</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>8.80362341660254</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>2.046184166263543</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>7.370478157664402</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>0.21739130434782608</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>0.44240097868256506</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>0.44240097868256506</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>0.41853490032280866</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>0.30106477792263103</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>0.7507505409389227</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>0.5769537857949623</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>0.0425531914893617</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>0.03520359637783018</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>0.03520359637783018</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>0.03520359637783018</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>0.03836073781154869</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>0.0004528714533858073</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>0.04358202279125211</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.17483811285846437</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>-0.4071973823047349</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-0.4071973823047349</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>-0.3833313039449785</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>-0.26270404011108234</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>-0.7502976694855369</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>-0.5333717630037101</t>
+          <t>Mechanism concordance is lower than status concordance because published coordinate labels and this study's architecture labels have different granularity.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>caller_validation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>event-class crosswalk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nzl_wp_only</t>
+          <t>published raw mechanism label versus repo prn event class among PRN-negative concordant rows</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>nzl_ap_with_prn</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1613-1614(IS insertion) -&gt; prn_evt_coding_disrupted_is481__is481__gap1043 (279); 1613-1614(IS insertion) -&gt; prn_evt_rearrangement__within_contig__cov58 (88); 245-246(IS insertion) -&gt; prn_evt_rearrangement__within_contig__cov91 (45); other -&gt; prn_evt_coding_disrupted_is481__is481__gap1043 (33); other -&gt; prn_evt_insufficient__not_available_current_step3 (19); other -&gt; prn_evt_rearrangement__within_contig__cov91 (8)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>figure_data/published_event_class_crosswalk.tsv</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.999</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.999</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>aipw_with_crossfit_when_available</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>increase</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1.0010010010010009</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-1.0010010010009715e-06</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>0.4509716886436216</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>0.45098039215686275</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>0.45097268964462256</t>
+          <t>Event-class comparison is reported as a crosswalk rather than a single concordance fraction because published labels are not one-to-one with the frozen event grammar.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>caller_validation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>manual/read junction evidence tiers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usa_wp_only</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>usa_ap_prn_background</t>
-        </is>
-      </c>
+          <t>event-class confidence tiers from read-backed TSD, public long-read or hybrid, assembly/rule support or unresolved validation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>561</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>0.972</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>tier_1_read_backed_tsd_recovered=561 genomes/6 event classes; tier_2_public_longread_or_hybrid=11 genomes/3 event classes; tier_3_assembly_or_rule_supported=3 genomes/3 event classes; tier_4_validation_unresolved=2 genomes/2 event classes</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>Supplementary Table 8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.9758956382983744</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.999</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0.34298467670641786</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>0.08244713220984862</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0.9427035156585314</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.9437170984967105</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>1.001001001001001</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.024700381388085</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>aipw_with_crossfit_when_available</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>mixed_or_zero</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>1.058745919845784</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>12.786280670164953</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>1.024700381388085</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>1.9437170984967105</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>0.0011086474501108647</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>0.2857142857142857</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>0.5247566699382887</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>0.5247566699382887</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>0.3449560799901752</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>0.287852410874605</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>0.99065749356738</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0.4061042396967595</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>0.5777525539160046</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>0.5597741581205131</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>0.5597741581205131</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>0.5693119693967906</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>0.577328683134091</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>0.23248385569616747</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0.5585142383063165</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.29203826820171885</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>0.03501748818222439</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>0.03501748818222439</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>0.22435588940661544</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>0.289476272259486</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>-0.7581736378712125</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>0.152409998609557</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="53" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>figure_label</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Figure 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>panel_label</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>panel_title</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Country glyph synthesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>final_placement</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>shared_input_bundle</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>original_bundle_label</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>manuscript/figure_data/selected_country/cross_country_evidence_grid.tsv</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>found</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>country_iso3</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>country_name</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>stage1_primary_default</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>stage2_triangulated_default</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>selection_state</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>narrative_role</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>vaccine_contrast_type</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>prevalence_direction</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>bounds_stability</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>repeated_origin_evidence</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>structural_reuse_evidence</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>package_anchor_completeness</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>amplification_pattern</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>final_interpretation_tier</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>screening_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>primary_and_triangulated</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>transition_country</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>wP_to_PRN-containing_aP</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>downward</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>bounds_narrow</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>insufficient_detection_window</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>biologically interesting but uncertain</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>triangulated_after_stage1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>JPN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>primary_and_triangulated</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PRN-free_or_PRN-removed_comparator</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>mixed_or_partial_PRN-exposed_to_PRN-free_or_removed</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>downward</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>bounds_mixed</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>insufficient_detection_window</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>compatible but bounded</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>triangulated_after_stage1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>primary_and_triangulated</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>transition_country</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>wP_to_PRN-containing_aP</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>upward</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>bounds_narrow</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>clear_post-origin_amplification</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>compatible but bounded</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>triangulated_after_stage1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>primary_and_triangulated</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>transition_country</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>wP_to_PRN-containing_aP</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>upward</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>bounds_narrow</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>package_anchor_complete</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>clear_post-origin_amplification</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>strongly selection-compatible</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>triangulated_after_stage1</t>
+          <t>Manual/read inspection validates architectures at event-class level; genome-level junction support is reported separately and is not assumed for every row in a supported class.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>read_validation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>primary disrupted-event families</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+          <t>resolved read/manual detectability for primary event-family audits</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>primary_only</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>transition_country</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>wP_to_PRN-containing_aP</t>
+          <t>0.960</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>uncertain_or_single_epoch_only</t>
+          <t>resolved primary families recovered 24/25 validation opportunities</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>figure_data/prn_event_class_detectability.tsv</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>epidemiologically estimable but not triangulated</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>stage1_primary_without_mechanistic_triangulation; no_country_specific_mechanism_layer</t>
+          <t>Supports recoverability of dominant event families without assuming genome-level junction support for every call.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>read_validation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>intact controls</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+          <t>read-validation audit of intact control rows</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>context_only</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>boundary_or_context_only</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>context_only</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>uncertain_or_single_epoch_only</t>
+          <t>0/7 resolved intact controls recovered an insertion-like validation signal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>figure_data/prn_event_class_detectability.tsv</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>insufficient_detection_window</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>context only</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>fails_default_stage1_screen; fewer_than_two_stage1_default_epochs</t>
+          <t>Bounds false-positive risk in the targeted validation set.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>threshold_sensitivity</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>event-definition hierarchy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+          <t>exact event grammar versus broader breakpoint and mechanism groupings</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>context_only</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>boundary_or_context_only</t>
+          <t>370-382</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>wP_to_mixed_or_uncertain_aP</t>
+          <t>0.641-0.662</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>uncertain_or_single_epoch_only</t>
+          <t>3-14 definitions; top-three share 0.943-1.000</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>Supplementary Fig. 14; Source Data</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>limited_or_nonpersistent_post-detection_change</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>context only</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>fails_default_stage1_screen; fewer_than_two_stage1_default_epochs</t>
+          <t>Structural concentration persists as event definitions are broadened.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>threshold_sensitivity</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>full caller threshold grid</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>HSP identity 85-95%, locus coverage 90-99% and relaxed/default/strict IS-support profiles</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>context_only</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>boundary_or_context_only</t>
+          <t>75</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>sustained_PRN-containing_aP</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>uncertain_or_single_epoch_only</t>
+          <t>structural disrupted 471-581; gap1043 338-359; cov58 108-108; cov91 0-62; top-three share 0.910-0.964; manuscript-status change fraction 0.000-0.071</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>Supplementary Fig. 15; Source Data</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>context only</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>fails_default_stage1_screen; fewer_than_two_stage1_default_epochs</t>
+          <t>Grid is a caller-side sensitivity layer before manuscript interpretability filters; gap1043 remained the dominant structural event in every threshold combination.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>threshold_sensitivity</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>IS support thresholds</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
+          <t>strong IS support at &gt;=80% query coverage and &gt;=90% identity; moderate at &gt;=60% and &gt;=85%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>context_only</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>boundary_or_context_only</t>
+          <t>382</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>wP_to_mixed_or_uncertain_aP</t>
+          <t>0.662</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>uncertain_or_single_epoch_only</t>
+          <t>none=175; strong=382; weak=20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>bounds_mixed</t>
+          <t>figure_data/prn_event_evidence_manifest.tsv</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>package_anchor_complete</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>insufficient_local_origin_window</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>context only</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>fails_default_stage1_screen; fewer_than_two_stage1_default_epochs</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="53" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="62" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>figure_label</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Figure 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>panel_label</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>panel_title</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Identifiability ledger</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>final_placement</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>shared_input_bundle</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>original_bundle_label</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>manuscript/figure_data/selected_country/cross_country_evidence_grid.tsv</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>found</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>country_iso3</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>country_name</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>stage1_primary_default</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>stage2_triangulated_default</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>selection_state</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>narrative_role</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>vaccine_contrast_type</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>prevalence_direction</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>bounds_stability</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>repeated_origin_evidence</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>structural_reuse_evidence</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
-        <is>
-          <t>package_anchor_completeness</t>
-        </is>
-      </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>amplification_pattern</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>final_interpretation_tier</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>screening_summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>primary_and_triangulated</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>transition_country</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>wP_to_PRN-containing_aP</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>downward</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>bounds_narrow</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>insufficient_detection_window</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>biologically interesting but uncertain</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>triangulated_after_stage1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>JPN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>primary_and_triangulated</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>PRN-free_or_PRN-removed_comparator</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>mixed_or_partial_PRN-exposed_to_PRN-free_or_removed</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>downward</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>bounds_mixed</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>insufficient_detection_window</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>compatible but bounded</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>triangulated_after_stage1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>primary_and_triangulated</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>transition_country</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>wP_to_PRN-containing_aP</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>upward</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>bounds_narrow</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>clear_post-origin_amplification</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>compatible but bounded</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>triangulated_after_stage1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>primary_and_triangulated</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>transition_country</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>wP_to_PRN-containing_aP</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>upward</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>bounds_narrow</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>package_anchor_complete</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>clear_post-origin_amplification</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>strongly selection-compatible</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>triangulated_after_stage1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GBR</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>primary_only</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>transition_country</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>wP_to_PRN-containing_aP</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>uncertain_or_single_epoch_only</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>bounds_mixed</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>epidemiologically estimable but not triangulated</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>stage1_primary_without_mechanistic_triangulation; no_country_specific_mechanism_layer</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>context_only</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>boundary_or_context_only</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>context_only</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>uncertain_or_single_epoch_only</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>bounds_mixed</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>insufficient_detection_window</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>context only</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>fails_default_stage1_screen; fewer_than_two_stage1_default_epochs</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CHN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>context_only</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>boundary_or_context_only</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>wP_to_mixed_or_uncertain_aP</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>uncertain_or_single_epoch_only</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>bounds_mixed</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>event_level_only</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>limited_or_nonpersistent_post-detection_change</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>context only</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>fails_default_stage1_screen; fewer_than_two_stage1_default_epochs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>context_only</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>boundary_or_context_only</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>sustained_PRN-containing_aP</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>uncertain_or_single_epoch_only</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>bounds_mixed</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>context only</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>fails_default_stage1_screen; fewer_than_two_stage1_default_epochs</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>context_only</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>boundary_or_context_only</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>wP_to_mixed_or_uncertain_aP</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>uncertain_or_single_epoch_only</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>bounds_mixed</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>not_observed</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>present</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>package_anchor_complete</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>insufficient_local_origin_window</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>context only</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>fails_default_stage1_screen; fewer_than_two_stage1_default_epochs</t>
+          <t>Strong and weak IS-support tiers are retained separately; non-IS rearrangement classes are not forced into IS support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>threshold_sensitivity</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HSP and split-structure thresholds</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>minimum HSP identity 90%; intact coverage &gt;=95%; disrupted union coverage &gt;=95%; insertion-like gap &gt;=50 bp</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>thresholds define recoverable full-length or split-locus structure; weaker patterns are retained as lower-confidence or non-interpretable</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Methods</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>The endpoint is recoverable-locus disruption, so threshold failures are not silently treated as intact PRN phenotype.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>false_negative_risk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>insufficient or assembly-gap rows</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>resolved detectability among insufficient-data validation rows</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.429</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6/14 insufficient-data validation rows were recovered; 8/14 remained true nonrecoveries</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>figure_data/prn_event_class_detectability.tsv</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Assembly gaps and incomplete local recovery remain explicit non-interpretable or false-negative risks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>false_negative_risk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mechanism classes outside split-HSP recovery</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>promoter inversion, small indel, premature stop, assembly gap and repeat-collapse risk</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>regulatory lesions and sub-HSP-scale coding changes may be missed unless captured by split structure, HSP disruption or external phenotype bridge</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Methods; Supplementary Table 10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Intact genome calls are genome-intact boundaries, not PRN-positive protein-expression assignments.</t>
         </is>
       </c>
     </row>
